--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/142.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/142.xlsx
@@ -426,13 +426,13 @@
         <v>-13.44845420527558</v>
       </c>
       <c r="E2">
-        <v>-29.14250294940335</v>
+        <v>-26.99472924009744</v>
       </c>
       <c r="F2">
-        <v>-5.282651272922951</v>
+        <v>-5.123812696280995</v>
       </c>
       <c r="G2">
-        <v>-17.44303385890047</v>
+        <v>-17.94774970018114</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.45964541666871</v>
       </c>
       <c r="E3">
-        <v>-28.83420896743516</v>
+        <v>-25.14905908879123</v>
       </c>
       <c r="F3">
-        <v>-5.153890439027021</v>
+        <v>-5.638713498332329</v>
       </c>
       <c r="G3">
-        <v>-18.46135104568921</v>
+        <v>-15.67152286956276</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.52462908944148</v>
       </c>
       <c r="E4">
-        <v>-30.6114697261445</v>
+        <v>-26.33266634017603</v>
       </c>
       <c r="F4">
-        <v>-5.218363898697518</v>
+        <v>-5.212737783432919</v>
       </c>
       <c r="G4">
-        <v>-17.50302922043591</v>
+        <v>-18.43861752947103</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.59694594026788</v>
       </c>
       <c r="E5">
-        <v>-29.84921660304039</v>
+        <v>-27.25479497388394</v>
       </c>
       <c r="F5">
-        <v>-5.119792458814652</v>
+        <v>-4.784297030276128</v>
       </c>
       <c r="G5">
-        <v>-18.17872149663778</v>
+        <v>-17.5396902017378</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.63121057198356</v>
       </c>
       <c r="E6">
-        <v>-30.14812079415367</v>
+        <v>-25.57509339495885</v>
       </c>
       <c r="F6">
-        <v>-5.065263088587198</v>
+        <v>-5.456690258941297</v>
       </c>
       <c r="G6">
-        <v>-18.18991776165159</v>
+        <v>-17.35373520352417</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.58679180044691</v>
       </c>
       <c r="E7">
-        <v>-30.65492949119611</v>
+        <v>-28.09225020059643</v>
       </c>
       <c r="F7">
-        <v>-4.990421106288318</v>
+        <v>-4.924687016709131</v>
       </c>
       <c r="G7">
-        <v>-17.24016693879947</v>
+        <v>-16.7995267064314</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.40896513030447</v>
       </c>
       <c r="E8">
-        <v>-30.85527823824346</v>
+        <v>-27.51530449812319</v>
       </c>
       <c r="F8">
-        <v>-4.915166568598467</v>
+        <v>-4.323377636205504</v>
       </c>
       <c r="G8">
-        <v>-18.53201795077049</v>
+        <v>-15.19110477726757</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.08204501344426</v>
       </c>
       <c r="E9">
-        <v>-31.50622373447604</v>
+        <v>-28.9302307302938</v>
       </c>
       <c r="F9">
-        <v>-5.183992729214736</v>
+        <v>-4.753082978535774</v>
       </c>
       <c r="G9">
-        <v>-17.95275027921821</v>
+        <v>-16.38888167192189</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.58814702994052</v>
       </c>
       <c r="E10">
-        <v>-31.73814726654187</v>
+        <v>-29.94050611056101</v>
       </c>
       <c r="F10">
-        <v>-5.304372591406161</v>
+        <v>-4.80586472928554</v>
       </c>
       <c r="G10">
-        <v>-17.06332752772822</v>
+        <v>-15.58640046738424</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.94107469038813</v>
       </c>
       <c r="E11">
-        <v>-31.85651704862837</v>
+        <v>-30.83681338547719</v>
       </c>
       <c r="F11">
-        <v>-4.862334931112365</v>
+        <v>-5.427337853504542</v>
       </c>
       <c r="G11">
-        <v>-17.50540784740588</v>
+        <v>-17.41640548585534</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.18725135163787</v>
       </c>
       <c r="E12">
-        <v>-32.05249581825831</v>
+        <v>-30.31795894757435</v>
       </c>
       <c r="F12">
-        <v>-4.844087471554671</v>
+        <v>-4.934819567156112</v>
       </c>
       <c r="G12">
-        <v>-17.50648377470614</v>
+        <v>-15.5826413429244</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.37149417329663</v>
       </c>
       <c r="E13">
-        <v>-34.14101444517386</v>
+        <v>-31.72578453250093</v>
       </c>
       <c r="F13">
-        <v>-4.912631847280806</v>
+        <v>-4.309060934729932</v>
       </c>
       <c r="G13">
-        <v>-15.90546091482258</v>
+        <v>-15.30839906099672</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.578454674823586</v>
       </c>
       <c r="E14">
-        <v>-33.31124403885239</v>
+        <v>-30.03550443829392</v>
       </c>
       <c r="F14">
-        <v>-4.884354778160635</v>
+        <v>-4.143235839442013</v>
       </c>
       <c r="G14">
-        <v>-15.80453396823959</v>
+        <v>-14.74429534328706</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.870092440326721</v>
       </c>
       <c r="E15">
-        <v>-33.74448314716621</v>
+        <v>-33.50075161912538</v>
       </c>
       <c r="F15">
-        <v>-4.549438985987162</v>
+        <v>-4.3478055080982</v>
       </c>
       <c r="G15">
-        <v>-16.00761276325511</v>
+        <v>-13.67682152105846</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.29758628874505</v>
       </c>
       <c r="E16">
-        <v>-35.02859082220324</v>
+        <v>-34.29649507175321</v>
       </c>
       <c r="F16">
-        <v>-4.542367739074725</v>
+        <v>-4.332083267622675</v>
       </c>
       <c r="G16">
-        <v>-15.27657313145493</v>
+        <v>-14.3138267620884</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.90060141728295</v>
       </c>
       <c r="E17">
-        <v>-34.05185332043684</v>
+        <v>-33.86339408189663</v>
       </c>
       <c r="F17">
-        <v>-4.289221058874264</v>
+        <v>-4.345577233875177</v>
       </c>
       <c r="G17">
-        <v>-15.51498537901109</v>
+        <v>-13.85772297150639</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.67128463390579</v>
       </c>
       <c r="E18">
-        <v>-35.95993942899077</v>
+        <v>-32.12814624079346</v>
       </c>
       <c r="F18">
-        <v>-4.152445089340294</v>
+        <v>-3.812024335404754</v>
       </c>
       <c r="G18">
-        <v>-14.66483397398071</v>
+        <v>-14.13390026730178</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.608268752750696</v>
       </c>
       <c r="E19">
-        <v>-36.40870441043989</v>
+        <v>-34.861954299906</v>
       </c>
       <c r="F19">
-        <v>-3.929526603947826</v>
+        <v>-3.060057803018331</v>
       </c>
       <c r="G19">
-        <v>-15.40155946774458</v>
+        <v>-13.30617284248165</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.677100815188266</v>
       </c>
       <c r="E20">
-        <v>-36.45867385687752</v>
+        <v>-34.96198602649843</v>
       </c>
       <c r="F20">
-        <v>-3.768823213590439</v>
+        <v>-3.807483058692231</v>
       </c>
       <c r="G20">
-        <v>-15.00015251056241</v>
+        <v>-14.61876773280175</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.835133334558893</v>
       </c>
       <c r="E21">
-        <v>-36.2952367014667</v>
+        <v>-35.6213114638822</v>
       </c>
       <c r="F21">
-        <v>-3.593438077543971</v>
+        <v>-3.620364245518272</v>
       </c>
       <c r="G21">
-        <v>-15.31696013176127</v>
+        <v>-13.99476300410452</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.048206450319444</v>
       </c>
       <c r="E22">
-        <v>-36.81805581836325</v>
+        <v>-36.84014571457266</v>
       </c>
       <c r="F22">
-        <v>-3.39474870895181</v>
+        <v>-3.252379090124508</v>
       </c>
       <c r="G22">
-        <v>-15.46521463737368</v>
+        <v>-13.43968052298938</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.262287596248783</v>
       </c>
       <c r="E23">
-        <v>-36.80394282911835</v>
+        <v>-34.54553623556804</v>
       </c>
       <c r="F23">
-        <v>-3.092179318248231</v>
+        <v>-2.50283483593575</v>
       </c>
       <c r="G23">
-        <v>-15.67778145590475</v>
+        <v>-14.20265533233414</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.450844171320327</v>
       </c>
       <c r="E24">
-        <v>-38.5627364708244</v>
+        <v>-36.34650129147053</v>
       </c>
       <c r="F24">
-        <v>-2.940698639289406</v>
+        <v>-2.637139432388676</v>
       </c>
       <c r="G24">
-        <v>-15.04075966214711</v>
+        <v>-13.18501018628987</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.584686217052766</v>
       </c>
       <c r="E25">
-        <v>-38.29643729256635</v>
+        <v>-36.130699126872</v>
       </c>
       <c r="F25">
-        <v>-2.725643253767094</v>
+        <v>-2.955911718313117</v>
       </c>
       <c r="G25">
-        <v>-14.84006942573818</v>
+        <v>-13.71667717880574</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.641669979567672</v>
       </c>
       <c r="E26">
-        <v>-38.20156123363164</v>
+        <v>-36.66389297772013</v>
       </c>
       <c r="F26">
-        <v>-3.035246674294098</v>
+        <v>-2.911754829978834</v>
       </c>
       <c r="G26">
-        <v>-15.10751350240097</v>
+        <v>-12.59692818723927</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.620241805067069</v>
       </c>
       <c r="E27">
-        <v>-38.19689916964074</v>
+        <v>-37.19506712916083</v>
       </c>
       <c r="F27">
-        <v>-2.755750295072556</v>
+        <v>-3.178813574793473</v>
       </c>
       <c r="G27">
-        <v>-15.40825339082499</v>
+        <v>-13.78444570126739</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.511087767738172</v>
       </c>
       <c r="E28">
-        <v>-38.80681216288982</v>
+        <v>-37.37885751099914</v>
       </c>
       <c r="F28">
-        <v>-3.023326119868586</v>
+        <v>-2.924241559269117</v>
       </c>
       <c r="G28">
-        <v>-14.71258693811192</v>
+        <v>-14.00524584655462</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.326809724419046</v>
       </c>
       <c r="E29">
-        <v>-38.11403715224839</v>
+        <v>-38.36221790600176</v>
       </c>
       <c r="F29">
-        <v>-3.323805810616743</v>
+        <v>-3.048039058826061</v>
       </c>
       <c r="G29">
-        <v>-15.40975968904535</v>
+        <v>-13.43348980283095</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.080094181058314</v>
       </c>
       <c r="E30">
-        <v>-37.22773554065217</v>
+        <v>-35.54744299586908</v>
       </c>
       <c r="F30">
-        <v>-3.037525627106416</v>
+        <v>-2.892617327696664</v>
       </c>
       <c r="G30">
-        <v>-15.11014373083192</v>
+        <v>-13.96955319982297</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.785940537151465</v>
       </c>
       <c r="E31">
-        <v>-36.98173298289649</v>
+        <v>-37.60290602676564</v>
       </c>
       <c r="F31">
-        <v>-2.882968599406849</v>
+        <v>-2.434054488028214</v>
       </c>
       <c r="G31">
-        <v>-14.95438090793644</v>
+        <v>-14.25221254378426</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.47306518288468</v>
       </c>
       <c r="E32">
-        <v>-37.91311102476506</v>
+        <v>-36.70180083363834</v>
       </c>
       <c r="F32">
-        <v>-3.398025396490855</v>
+        <v>-2.651078420003417</v>
       </c>
       <c r="G32">
-        <v>-14.9839076636012</v>
+        <v>-11.60590975896737</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.154605574921656</v>
       </c>
       <c r="E33">
-        <v>-37.38334070026674</v>
+        <v>-35.94649438966199</v>
       </c>
       <c r="F33">
-        <v>-2.879183542268949</v>
+        <v>-2.113871911986075</v>
       </c>
       <c r="G33">
-        <v>-14.08955054398493</v>
+        <v>-13.97640271854372</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.854041797777563</v>
       </c>
       <c r="E34">
-        <v>-37.0159274901284</v>
+        <v>-35.07273665106702</v>
       </c>
       <c r="F34">
-        <v>-2.888592339112575</v>
+        <v>-2.985185730307057</v>
       </c>
       <c r="G34">
-        <v>-14.35938980034539</v>
+        <v>-14.240157192203</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.586846136602712</v>
       </c>
       <c r="E35">
-        <v>-36.70546210487354</v>
+        <v>-34.71279315880435</v>
       </c>
       <c r="F35">
-        <v>-3.019094457662531</v>
+        <v>-3.024903490960363</v>
       </c>
       <c r="G35">
-        <v>-14.65538898755717</v>
+        <v>-14.37919182848854</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.357360006262723</v>
       </c>
       <c r="E36">
-        <v>-36.85792223928978</v>
+        <v>-36.20653748107846</v>
       </c>
       <c r="F36">
-        <v>-3.285578317229866</v>
+        <v>-2.871309356457384</v>
       </c>
       <c r="G36">
-        <v>-15.23078166555573</v>
+        <v>-14.40606187135804</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.180726945113919</v>
       </c>
       <c r="E37">
-        <v>-36.11927378695065</v>
+        <v>-35.01230416543466</v>
       </c>
       <c r="F37">
-        <v>-3.162702534515707</v>
+        <v>-3.28348624171557</v>
       </c>
       <c r="G37">
-        <v>-15.1303860615318</v>
+        <v>-14.34573214472313</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.05155978050124</v>
       </c>
       <c r="E38">
-        <v>-35.53682146008408</v>
+        <v>-35.42002985118926</v>
       </c>
       <c r="F38">
-        <v>-3.652565737896902</v>
+        <v>-2.370874916090631</v>
       </c>
       <c r="G38">
-        <v>-15.81694354819355</v>
+        <v>-13.62543688847066</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.973032929738442</v>
       </c>
       <c r="E39">
-        <v>-35.60120277505114</v>
+        <v>-35.25475187109431</v>
       </c>
       <c r="F39">
-        <v>-3.281307062375925</v>
+        <v>-2.918206847878335</v>
       </c>
       <c r="G39">
-        <v>-14.49815462716948</v>
+        <v>-12.59308133332264</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.94406812952127</v>
       </c>
       <c r="E40">
-        <v>-36.04591250802639</v>
+        <v>-33.58505595548917</v>
       </c>
       <c r="F40">
-        <v>-3.434696106962855</v>
+        <v>-2.831393632564648</v>
       </c>
       <c r="G40">
-        <v>-14.36182967240783</v>
+        <v>-14.1010927610076</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.951920642687767</v>
       </c>
       <c r="E41">
-        <v>-35.19767045622763</v>
+        <v>-33.02279609422282</v>
       </c>
       <c r="F41">
-        <v>-3.444321079663939</v>
+        <v>-2.359163410845956</v>
       </c>
       <c r="G41">
-        <v>-16.04449389583536</v>
+        <v>-13.85309813938803</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.001316461733646</v>
       </c>
       <c r="E42">
-        <v>-34.47033413195967</v>
+        <v>-33.27514757253725</v>
       </c>
       <c r="F42">
-        <v>-3.216854190882328</v>
+        <v>-2.900306219916122</v>
       </c>
       <c r="G42">
-        <v>-14.4333043506007</v>
+        <v>-13.7793209767726</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.07985799008219</v>
       </c>
       <c r="E43">
-        <v>-34.22597767450577</v>
+        <v>-32.05943344043806</v>
       </c>
       <c r="F43">
-        <v>-3.255638356898483</v>
+        <v>-2.421574093561594</v>
       </c>
       <c r="G43">
-        <v>-15.34046997090841</v>
+        <v>-11.96094590478097</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.18501590905278</v>
       </c>
       <c r="E44">
-        <v>-33.04676304290841</v>
+        <v>-31.83828314803648</v>
       </c>
       <c r="F44">
-        <v>-2.936784510119397</v>
+        <v>-2.420433825302477</v>
       </c>
       <c r="G44">
-        <v>-15.06384409619245</v>
+        <v>-14.09842942712126</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.318182692354664</v>
       </c>
       <c r="E45">
-        <v>-32.3111962171315</v>
+        <v>-30.89620885056179</v>
       </c>
       <c r="F45">
-        <v>-3.020310743805589</v>
+        <v>-2.659281224792435</v>
       </c>
       <c r="G45">
-        <v>-15.14841860308421</v>
+        <v>-14.44160223299488</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.46843830660774</v>
       </c>
       <c r="E46">
-        <v>-33.60589372863547</v>
+        <v>-31.41196128376937</v>
       </c>
       <c r="F46">
-        <v>-2.938186881707519</v>
+        <v>-3.352395661655213</v>
       </c>
       <c r="G46">
-        <v>-14.37671719569794</v>
+        <v>-13.22190952687058</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.647263559765634</v>
       </c>
       <c r="E47">
-        <v>-32.13477592674068</v>
+        <v>-31.51969141617485</v>
       </c>
       <c r="F47">
-        <v>-3.387858004513733</v>
+        <v>-2.578884393995152</v>
       </c>
       <c r="G47">
-        <v>-14.64574205785573</v>
+        <v>-12.289464580825</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.852209414121762</v>
       </c>
       <c r="E48">
-        <v>-32.75670749000611</v>
+        <v>-31.0664840017242</v>
       </c>
       <c r="F48">
-        <v>-3.235541128831556</v>
+        <v>-2.03435403797186</v>
       </c>
       <c r="G48">
-        <v>-14.61734916403817</v>
+        <v>-13.68402195760637</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.086847392425938</v>
       </c>
       <c r="E49">
-        <v>-31.78488564677503</v>
+        <v>-31.58331421174561</v>
       </c>
       <c r="F49">
-        <v>-3.216254758193335</v>
+        <v>-2.828985607720222</v>
       </c>
       <c r="G49">
-        <v>-15.30509679182129</v>
+        <v>-13.3178855525996</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.362350123186242</v>
       </c>
       <c r="E50">
-        <v>-31.81113041788649</v>
+        <v>-27.53742609365066</v>
       </c>
       <c r="F50">
-        <v>-3.232944642983193</v>
+        <v>-3.064998173621544</v>
       </c>
       <c r="G50">
-        <v>-14.24495251741663</v>
+        <v>-13.71196296195782</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.670504645757557</v>
       </c>
       <c r="E51">
-        <v>-30.55950322266947</v>
+        <v>-27.6733572979389</v>
       </c>
       <c r="F51">
-        <v>-2.9246501553953</v>
+        <v>-2.280152322724682</v>
       </c>
       <c r="G51">
-        <v>-14.92732712978952</v>
+        <v>-13.42552131971792</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.024180279217088</v>
       </c>
       <c r="E52">
-        <v>-30.93360725315414</v>
+        <v>-28.38296917494085</v>
       </c>
       <c r="F52">
-        <v>-3.511322133975477</v>
+        <v>-2.268123284443961</v>
       </c>
       <c r="G52">
-        <v>-14.44146319008223</v>
+        <v>-13.88551665658134</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.419091800883859</v>
       </c>
       <c r="E53">
-        <v>-30.05434289016583</v>
+        <v>-29.63436315374647</v>
       </c>
       <c r="F53">
-        <v>-2.991967159036969</v>
+        <v>-2.672668290895645</v>
       </c>
       <c r="G53">
-        <v>-14.89385089329641</v>
+        <v>-13.32500984660011</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.849843790523815</v>
       </c>
       <c r="E54">
-        <v>-29.9733828318567</v>
+        <v>-27.97930100189711</v>
       </c>
       <c r="F54">
-        <v>-2.976176027354122</v>
+        <v>-3.03031501407342</v>
       </c>
       <c r="G54">
-        <v>-15.73859617746116</v>
+        <v>-13.04444773323795</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.320449274272379</v>
       </c>
       <c r="E55">
-        <v>-29.85778900433691</v>
+        <v>-27.10080421525311</v>
       </c>
       <c r="F55">
-        <v>-3.305707219415101</v>
+        <v>-2.935622861830422</v>
       </c>
       <c r="G55">
-        <v>-14.82689842031019</v>
+        <v>-12.8152917710096</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.810539215090959</v>
       </c>
       <c r="E56">
-        <v>-28.41433338591797</v>
+        <v>-26.44672048653322</v>
       </c>
       <c r="F56">
-        <v>-3.443201399581723</v>
+        <v>-2.806863611640407</v>
       </c>
       <c r="G56">
-        <v>-15.36555231918669</v>
+        <v>-13.15763859577118</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.32166550652281</v>
       </c>
       <c r="E57">
-        <v>-29.43377439757671</v>
+        <v>-25.46050488866876</v>
       </c>
       <c r="F57">
-        <v>-2.676439094680306</v>
+        <v>-3.092929202999191</v>
       </c>
       <c r="G57">
-        <v>-15.44916180205376</v>
+        <v>-14.55844131671238</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.83940049750503</v>
       </c>
       <c r="E58">
-        <v>-28.23341179236353</v>
+        <v>-26.06978842403077</v>
       </c>
       <c r="F58">
-        <v>-3.077811938183364</v>
+        <v>-2.802685795435477</v>
       </c>
       <c r="G58">
-        <v>-15.85322712730396</v>
+        <v>-13.50097858419453</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.34716199730622</v>
       </c>
       <c r="E59">
-        <v>-29.27948928813538</v>
+        <v>-26.40878545977096</v>
       </c>
       <c r="F59">
-        <v>-3.051220724010178</v>
+        <v>-2.56378930106214</v>
       </c>
       <c r="G59">
-        <v>-15.92610713207825</v>
+        <v>-13.21872478206181</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.84427277149762</v>
       </c>
       <c r="E60">
-        <v>-28.34382957409255</v>
+        <v>-26.06937180442206</v>
       </c>
       <c r="F60">
-        <v>-2.67957720795175</v>
+        <v>-2.922336361052843</v>
       </c>
       <c r="G60">
-        <v>-14.8163278484033</v>
+        <v>-13.61004781753136</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.30657632846306</v>
       </c>
       <c r="E61">
-        <v>-28.7207027664329</v>
+        <v>-24.95517700262683</v>
       </c>
       <c r="F61">
-        <v>-2.812088257455441</v>
+        <v>-2.03837189987933</v>
       </c>
       <c r="G61">
-        <v>-16.21611257659118</v>
+        <v>-13.81484147513621</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.73745696525313</v>
       </c>
       <c r="E62">
-        <v>-28.52224692152076</v>
+        <v>-26.83001052654244</v>
       </c>
       <c r="F62">
-        <v>-2.88274608872573</v>
+        <v>-3.265367854189985</v>
       </c>
       <c r="G62">
-        <v>-15.92724099392545</v>
+        <v>-15.74768362496646</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.12815882229482</v>
       </c>
       <c r="E63">
-        <v>-28.99040962138173</v>
+        <v>-23.78737865400281</v>
       </c>
       <c r="F63">
-        <v>-3.494530100154073</v>
+        <v>-2.984269556434976</v>
       </c>
       <c r="G63">
-        <v>-16.50461503342927</v>
+        <v>-16.13066077513151</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.46933681085204</v>
       </c>
       <c r="E64">
-        <v>-27.59685325805332</v>
+        <v>-24.51084313299422</v>
       </c>
       <c r="F64">
-        <v>-2.994942150599122</v>
+        <v>-2.966047436171929</v>
       </c>
       <c r="G64">
-        <v>-16.07358697003447</v>
+        <v>-16.266361692059</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.77014794551844</v>
       </c>
       <c r="E65">
-        <v>-27.47383273316095</v>
+        <v>-24.49369380192717</v>
       </c>
       <c r="F65">
-        <v>-3.050519934142596</v>
+        <v>-3.254279537223036</v>
       </c>
       <c r="G65">
-        <v>-15.7239023210851</v>
+        <v>-14.22052896770066</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.0144944835972</v>
       </c>
       <c r="E66">
-        <v>-27.43989182047346</v>
+        <v>-23.83394948069769</v>
       </c>
       <c r="F66">
-        <v>-3.425220002617823</v>
+        <v>-2.861778614258269</v>
       </c>
       <c r="G66">
-        <v>-16.6663500804776</v>
+        <v>-16.15239781714236</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.21433677516995</v>
       </c>
       <c r="E67">
-        <v>-28.04977311440448</v>
+        <v>-25.72178425348932</v>
       </c>
       <c r="F67">
-        <v>-3.102251687870426</v>
+        <v>-3.115067036138162</v>
       </c>
       <c r="G67">
-        <v>-16.25527301977521</v>
+        <v>-16.4239767651837</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.36731708825051</v>
       </c>
       <c r="E68">
-        <v>-26.87926673832387</v>
+        <v>-25.8658259547253</v>
       </c>
       <c r="F68">
-        <v>-2.9588487009333</v>
+        <v>-2.898097742017042</v>
       </c>
       <c r="G68">
-        <v>-16.35933339771113</v>
+        <v>-14.39170569062699</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.46788725498402</v>
       </c>
       <c r="E69">
-        <v>-27.56731402210129</v>
+        <v>-24.80834576140213</v>
       </c>
       <c r="F69">
-        <v>-3.319419737083933</v>
+        <v>-2.770276837581924</v>
       </c>
       <c r="G69">
-        <v>-16.62890118933736</v>
+        <v>-15.00724700965307</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.53165261380517</v>
       </c>
       <c r="E70">
-        <v>-27.69813710770887</v>
+        <v>-24.26779993300255</v>
       </c>
       <c r="F70">
-        <v>-3.372398659220171</v>
+        <v>-2.635090908787055</v>
       </c>
       <c r="G70">
-        <v>-16.47711598690731</v>
+        <v>-14.93522112562791</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.54748564896842</v>
       </c>
       <c r="E71">
-        <v>-27.85292487776506</v>
+        <v>-25.22730206269576</v>
       </c>
       <c r="F71">
-        <v>-3.797688629458196</v>
+        <v>-3.330015521511181</v>
       </c>
       <c r="G71">
-        <v>-16.19756358993464</v>
+        <v>-14.14245968279357</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.53189988633327</v>
       </c>
       <c r="E72">
-        <v>-27.39320778192839</v>
+        <v>-25.02966134310499</v>
       </c>
       <c r="F72">
-        <v>-3.157464427200392</v>
+        <v>-2.423368432363787</v>
       </c>
       <c r="G72">
-        <v>-16.37420933409184</v>
+        <v>-15.07663935470173</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.48809075588946</v>
       </c>
       <c r="E73">
-        <v>-28.15492428086258</v>
+        <v>-26.36264483810681</v>
       </c>
       <c r="F73">
-        <v>-3.845533968869537</v>
+        <v>-3.262414242657691</v>
       </c>
       <c r="G73">
-        <v>-16.5457386301181</v>
+        <v>-15.33228630233533</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.4131107222756</v>
       </c>
       <c r="E74">
-        <v>-27.89921041059745</v>
+        <v>-23.63917981362779</v>
       </c>
       <c r="F74">
-        <v>-3.836964536161094</v>
+        <v>-3.124696759956991</v>
       </c>
       <c r="G74">
-        <v>-16.6725209373628</v>
+        <v>-15.66269198933675</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.32602765627815</v>
       </c>
       <c r="E75">
-        <v>-28.42640629762242</v>
+        <v>-25.38683114503797</v>
       </c>
       <c r="F75">
-        <v>-3.614631230104381</v>
+        <v>-3.56142425431632</v>
       </c>
       <c r="G75">
-        <v>-15.87636453007793</v>
+        <v>-14.46737814056365</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.21617678640391</v>
       </c>
       <c r="E76">
-        <v>-28.40473754949572</v>
+        <v>-25.3134653376397</v>
       </c>
       <c r="F76">
-        <v>-3.519397450438303</v>
+        <v>-3.64901744479336</v>
       </c>
       <c r="G76">
-        <v>-15.53934768363458</v>
+        <v>-15.22850897604302</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.09988046792566</v>
       </c>
       <c r="E77">
-        <v>-29.37117277289467</v>
+        <v>-26.24555208569048</v>
       </c>
       <c r="F77">
-        <v>-4.204642452607263</v>
+        <v>-3.384473624972439</v>
       </c>
       <c r="G77">
-        <v>-15.19482748572648</v>
+        <v>-14.10438178800087</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.98176703506392</v>
       </c>
       <c r="E78">
-        <v>-28.05832740180497</v>
+        <v>-25.01569100079133</v>
       </c>
       <c r="F78">
-        <v>-4.068480169115525</v>
+        <v>-3.32002867200842</v>
       </c>
       <c r="G78">
-        <v>-15.55449674002229</v>
+        <v>-15.58193454145177</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.85755966273693</v>
       </c>
       <c r="E79">
-        <v>-29.43244981892947</v>
+        <v>-26.38159650182891</v>
       </c>
       <c r="F79">
-        <v>-3.953403346181949</v>
+        <v>-3.915725398747729</v>
       </c>
       <c r="G79">
-        <v>-15.66330609553428</v>
+        <v>-12.63844904939281</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.74891344447326</v>
       </c>
       <c r="E80">
-        <v>-29.70054680136857</v>
+        <v>-26.96404882869547</v>
       </c>
       <c r="F80">
-        <v>-4.244582723941688</v>
+        <v>-3.479407292367542</v>
       </c>
       <c r="G80">
-        <v>-15.59620630327157</v>
+        <v>-14.16448308699357</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.64656461130802</v>
       </c>
       <c r="E81">
-        <v>-30.5536750766216</v>
+        <v>-26.16689249217724</v>
       </c>
       <c r="F81">
-        <v>-3.679377879045292</v>
+        <v>-3.233574957937538</v>
       </c>
       <c r="G81">
-        <v>-15.53710809957727</v>
+        <v>-13.24430536744375</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.56580248661087</v>
       </c>
       <c r="E82">
-        <v>-31.22621912963376</v>
+        <v>-28.50155632377971</v>
       </c>
       <c r="F82">
-        <v>-3.720612829965589</v>
+        <v>-3.81813744023835</v>
       </c>
       <c r="G82">
-        <v>-14.92279499294626</v>
+        <v>-12.93198519072337</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.51272698748696</v>
       </c>
       <c r="E83">
-        <v>-30.89400348372005</v>
+        <v>-31.53142922080273</v>
       </c>
       <c r="F83">
-        <v>-4.550496109685718</v>
+        <v>-3.680519731010324</v>
       </c>
       <c r="G83">
-        <v>-14.62619328644633</v>
+        <v>-13.55793817547046</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.47741161389454</v>
       </c>
       <c r="E84">
-        <v>-32.2643785886032</v>
+        <v>-30.20717888792471</v>
       </c>
       <c r="F84">
-        <v>-4.308310258126014</v>
+        <v>-3.738019341682184</v>
       </c>
       <c r="G84">
-        <v>-15.41806253725784</v>
+        <v>-14.26813626782815</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.47913172503647</v>
       </c>
       <c r="E85">
-        <v>-33.06688531716149</v>
+        <v>-30.28724004414331</v>
       </c>
       <c r="F85">
-        <v>-3.801027081527943</v>
+        <v>-3.881989295337038</v>
       </c>
       <c r="G85">
-        <v>-15.11988997689954</v>
+        <v>-13.47926802654799</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.50491879427237</v>
       </c>
       <c r="E86">
-        <v>-33.56055917534469</v>
+        <v>-32.90706414824579</v>
       </c>
       <c r="F86">
-        <v>-4.159378553838088</v>
+        <v>-3.825651332954153</v>
       </c>
       <c r="G86">
-        <v>-14.66394840304895</v>
+        <v>-11.85656771447328</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.56350019154326</v>
       </c>
       <c r="E87">
-        <v>-34.45143228145165</v>
+        <v>-33.77016185902671</v>
       </c>
       <c r="F87">
-        <v>-4.091634741452208</v>
+        <v>-3.665877577969129</v>
       </c>
       <c r="G87">
-        <v>-13.33083971729477</v>
+        <v>-12.89979675644504</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.66115322952584</v>
       </c>
       <c r="E88">
-        <v>-33.9833443014118</v>
+        <v>-31.75802047472453</v>
       </c>
       <c r="F88">
-        <v>-4.128891423112921</v>
+        <v>-3.966150595095321</v>
       </c>
       <c r="G88">
-        <v>-14.40664287210018</v>
+        <v>-11.88820328764656</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.7842838064758</v>
       </c>
       <c r="E89">
-        <v>-36.66876108727838</v>
+        <v>-33.05613245563028</v>
       </c>
       <c r="F89">
-        <v>-4.473845535231407</v>
+        <v>-4.624064792428585</v>
       </c>
       <c r="G89">
-        <v>-13.52413419496896</v>
+        <v>-11.93245203932446</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.95569604923092</v>
       </c>
       <c r="E90">
-        <v>-36.55197400685756</v>
+        <v>-33.96702368108816</v>
       </c>
       <c r="F90">
-        <v>-4.410116417341166</v>
+        <v>-3.721296990921059</v>
       </c>
       <c r="G90">
-        <v>-14.79187450377747</v>
+        <v>-12.52668503198702</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-14.16522066183894</v>
       </c>
       <c r="E91">
-        <v>-37.00359192693151</v>
+        <v>-35.96147684591637</v>
       </c>
       <c r="F91">
-        <v>-4.539694443489463</v>
+        <v>-4.230272357289777</v>
       </c>
       <c r="G91">
-        <v>-14.44900626809346</v>
+        <v>-13.9242616263002</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-14.4187621050152</v>
       </c>
       <c r="E92">
-        <v>-39.28841763784256</v>
+        <v>-35.50752223325446</v>
       </c>
       <c r="F92">
-        <v>-4.710203349022294</v>
+        <v>-5.356285679461309</v>
       </c>
       <c r="G92">
-        <v>-14.49556909110331</v>
+        <v>-13.00227469361318</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-14.72163996571409</v>
       </c>
       <c r="E93">
-        <v>-40.95206577641046</v>
+        <v>-38.27849095007394</v>
       </c>
       <c r="F93">
-        <v>-4.812752266311787</v>
+        <v>-4.23627222715042</v>
       </c>
       <c r="G93">
-        <v>-14.28754103050659</v>
+        <v>-13.70428249630671</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-15.04782849153013</v>
       </c>
       <c r="E94">
-        <v>-42.12407334162462</v>
+        <v>-41.04810112469113</v>
       </c>
       <c r="F94">
-        <v>-4.990829702414501</v>
+        <v>-4.129915288987252</v>
       </c>
       <c r="G94">
-        <v>-14.68010386528059</v>
+        <v>-12.61928761181151</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-15.40538131334526</v>
       </c>
       <c r="E95">
-        <v>-43.66431603500949</v>
+        <v>-39.42337295598215</v>
       </c>
       <c r="F95">
-        <v>-5.03962764093398</v>
+        <v>-4.143809140983403</v>
       </c>
       <c r="G95">
-        <v>-14.48313799260335</v>
+        <v>-13.50215051731543</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-15.76241541187271</v>
       </c>
       <c r="E96">
-        <v>-43.98752454612194</v>
+        <v>-43.27613977154599</v>
       </c>
       <c r="F96">
-        <v>-5.056499651904114</v>
+        <v>-5.178778377488151</v>
       </c>
       <c r="G96">
-        <v>-14.90905953950382</v>
+        <v>-12.74380385063458</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-16.10096497722452</v>
       </c>
       <c r="E97">
-        <v>-45.51529129361568</v>
+        <v>-44.00022012300244</v>
       </c>
       <c r="F97">
-        <v>-4.897140827868935</v>
+        <v>-5.122715188081595</v>
       </c>
       <c r="G97">
-        <v>-14.8544653330157</v>
+        <v>-14.00250140430257</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-16.40138430510699</v>
       </c>
       <c r="E98">
-        <v>-48.82668243791804</v>
+        <v>-47.18235390158537</v>
       </c>
       <c r="F98">
-        <v>-5.506554823394823</v>
+        <v>-5.17067376246589</v>
       </c>
       <c r="G98">
-        <v>-14.26085803346006</v>
+        <v>-13.41478190998853</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-16.62779138991433</v>
       </c>
       <c r="E99">
-        <v>-49.05642664186768</v>
+        <v>-48.25352593607072</v>
       </c>
       <c r="F99">
-        <v>-5.484619704613029</v>
+        <v>-4.50006932963221</v>
       </c>
       <c r="G99">
-        <v>-14.8667689755124</v>
+        <v>-12.87142538117348</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-16.76873806020517</v>
       </c>
       <c r="E100">
-        <v>-50.48600248745311</v>
+        <v>-51.24102137332996</v>
       </c>
       <c r="F100">
-        <v>-6.124466984862959</v>
+        <v>-5.31730513391164</v>
       </c>
       <c r="G100">
-        <v>-15.06059976156396</v>
+        <v>-13.82836836420967</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-16.81757697744991</v>
       </c>
       <c r="E101">
-        <v>-51.55847079762316</v>
+        <v>-52.49574038417571</v>
       </c>
       <c r="F101">
-        <v>-6.029827886768128</v>
+        <v>-5.191319744632517</v>
       </c>
       <c r="G101">
-        <v>-14.78669184473574</v>
+        <v>-15.18984014887157</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-16.73662934621155</v>
       </c>
       <c r="E102">
-        <v>-53.93830615745214</v>
+        <v>-55.05055937601658</v>
       </c>
       <c r="F102">
-        <v>-6.319165810474691</v>
+        <v>-4.872679698152015</v>
       </c>
       <c r="G102">
-        <v>-15.0815687570097</v>
+        <v>-13.9004554933273</v>
       </c>
     </row>
   </sheetData>
